--- a/data/data_monitoreo_la_peñita.xlsx
+++ b/data/data_monitoreo_la_peñita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,117 +443,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PEREZ VEGA ANA YSABEL</t>
+          <t>GARAVITO LEON IVONNE LISSETH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZAPATA ZETA ROSA ARACELI</t>
+          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>137</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GARAVITO LEON IVONNE LISSETH</t>
+          <t>ZAPATA ZETA ROSA ARACELI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
+          <t>PEREZ VEGA ANA YSABEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>133</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PANTA MONZON SHIRLEY MARIBEL</t>
+          <t>NIÑO GUERRERO ANYELA MELINA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>126</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIÑO GUERRERO ANYELA MELINA</t>
+          <t>VALLE SILVA SUTMMER ORFELINDA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VALLE SILVA SUTMMER ORFELINDA</t>
+          <t>TIZON NUÑEZ FRESIA YAMILI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TIZON NUÑEZ FRESIA YAMILI</t>
+          <t>PANTA MONZON SHIRLEY MARIBEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CASTRO JUAREZ MARIA ISABEL</t>
+          <t>MORENO PALACIOS DAMARIS VANESA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MORENO PALACIOS DAMARIS VANESA</t>
+          <t>CHERO JUAREZ ANYELA TATIANA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHERO JUAREZ ANYELA TATIANA</t>
+          <t>CASTRO JUAREZ MARIA ISABEL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>71050834</t>
+          <t>77911713</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -563,10 +563,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>71050834</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>MORETO ESPINOZA JUAN ALBERTO</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/data_monitoreo_la_peñita.xlsx
+++ b/data/data_monitoreo_la_peñita.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
@@ -457,27 +457,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ZAPATA ZETA ROSA ARACELI</t>
+          <t>PEREZ VEGA ANA YSABEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PEREZ VEGA ANA YSABEL</t>
+          <t>ZAPATA ZETA ROSA ARACELI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
@@ -507,47 +507,47 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PANTA MONZON SHIRLEY MARIBEL</t>
+          <t>CASTRO JUAREZ MARIA ISABEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MORENO PALACIOS DAMARIS VANESA</t>
+          <t>PANTA MONZON SHIRLEY MARIBEL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHERO JUAREZ ANYELA TATIANA</t>
+          <t>MORENO PALACIOS DAMARIS VANESA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CASTRO JUAREZ MARIA ISABEL</t>
+          <t>CHERO JUAREZ ANYELA TATIANA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">

--- a/data/data_monitoreo_la_peñita.xlsx
+++ b/data/data_monitoreo_la_peñita.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5">
@@ -477,27 +477,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIÑO GUERRERO ANYELA MELINA</t>
+          <t>VALLE SILVA SUTMMER ORFELINDA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALLE SILVA SUTMMER ORFELINDA</t>
+          <t>NIÑO GUERRERO ANYELA MELINA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
@@ -507,27 +507,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CASTRO JUAREZ MARIA ISABEL</t>
+          <t>PANTA MONZON SHIRLEY MARIBEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PANTA MONZON SHIRLEY MARIBEL</t>
+          <t>CASTRO JUAREZ MARIA ISABEL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">

--- a/data/data_monitoreo_la_peñita.xlsx
+++ b/data/data_monitoreo_la_peñita.xlsx
@@ -443,61 +443,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GARAVITO LEON IVONNE LISSETH</t>
+          <t>ZAPATA ZETA ROSA ARACELI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
+          <t>GARAVITO LEON IVONNE LISSETH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>239</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PEREZ VEGA ANA YSABEL</t>
+          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>238</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZAPATA ZETA ROSA ARACELI</t>
+          <t>PEREZ VEGA ANA YSABEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALLE SILVA SUTMMER ORFELINDA</t>
+          <t>NIÑO GUERRERO ANYELA MELINA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIÑO GUERRERO ANYELA MELINA</t>
+          <t>VALLE SILVA SUTMMER ORFELINDA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
@@ -507,37 +507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PANTA MONZON SHIRLEY MARIBEL</t>
+          <t>MORENO PALACIOS DAMARIS VANESA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CASTRO JUAREZ MARIA ISABEL</t>
+          <t>PANTA MONZON SHIRLEY MARIBEL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MORENO PALACIOS DAMARIS VANESA</t>
+          <t>CASTRO JUAREZ MARIA ISABEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>156</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">

--- a/data/data_monitoreo_la_peñita.xlsx
+++ b/data/data_monitoreo_la_peñita.xlsx
@@ -443,41 +443,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ZAPATA ZETA ROSA ARACELI</t>
+          <t>PEREZ VEGA ANA YSABEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GARAVITO LEON IVONNE LISSETH</t>
+          <t>ZAPATA ZETA ROSA ARACELI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
+          <t>GARAVITO LEON IVONNE LISSETH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PEREZ VEGA ANA YSABEL</t>
+          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">

--- a/data/data_monitoreo_la_peñita.xlsx
+++ b/data/data_monitoreo_la_peñita.xlsx
@@ -513,31 +513,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MORENO PALACIOS DAMARIS VANESA</t>
+          <t>CASTRO JUAREZ MARIA ISABEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PANTA MONZON SHIRLEY MARIBEL</t>
+          <t>MORENO PALACIOS DAMARIS VANESA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CASTRO JUAREZ MARIA ISABEL</t>
+          <t>PANTA MONZON SHIRLEY MARIBEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>189</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
